--- a/evaluador-front/src/assets/plantillamovilidadbog.xlsx
+++ b/evaluador-front/src/assets/plantillamovilidadbog.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develoment\cursos\UniServerZ\www\elevaluador\evaluador-front\src\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>Ubicación</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>Activo</t>
+  </si>
+  <si>
+    <t>Caja de cambios</t>
+  </si>
+  <si>
+    <t>Manual</t>
   </si>
 </sst>
 </file>
@@ -496,14 +502,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,8 +588,11 @@
       <c r="Z1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -649,6 +658,9 @@
       </c>
       <c r="Z2" t="s">
         <v>33</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/evaluador-front/src/assets/plantillamovilidadbog.xlsx
+++ b/evaluador-front/src/assets/plantillamovilidadbog.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develoment\cursos\UniServerZ\www\elevaluador\evaluador-front\src\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATOS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19344" windowHeight="4704"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Ubicación</t>
   </si>
@@ -98,9 +98,6 @@
     <t>PATIO ALAMOS</t>
   </si>
   <si>
-    <t>AKT123</t>
-  </si>
-  <si>
     <t>DUCATI</t>
   </si>
   <si>
@@ -147,6 +144,21 @@
   </si>
   <si>
     <t>Manual</t>
+  </si>
+  <si>
+    <t>Prueba Limitacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cod Fasecolda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha ingreso a patios </t>
+  </si>
+  <si>
+    <t>limitacion1</t>
+  </si>
+  <si>
+    <t>XPX85H</t>
   </si>
 </sst>
 </file>
@@ -502,25 +514,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
@@ -589,24 +601,33 @@
         <v>22</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2">
         <v>42695</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2">
         <v>45987</v>
@@ -615,19 +636,19 @@
         <v>45987</v>
       </c>
       <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
       </c>
       <c r="M2">
         <v>1103</v>
@@ -645,21 +666,30 @@
         <v>1321321321</v>
       </c>
       <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
         <v>30</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>31</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>32</v>
       </c>
-      <c r="U2" t="s">
-        <v>33</v>
-      </c>
       <c r="Z2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2">
+        <v>123456</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>45731</v>
+      </c>
+      <c r="AD2" t="s">
         <v>40</v>
       </c>
     </row>
